--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_39_R4.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_39_R4.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8772</v>
+        <v>4.7987</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6896</v>
+        <v>5.3422</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8124</v>
+        <v>-0.5435</v>
       </c>
       <c r="G2" t="n">
         <v>3.896</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6581</v>
+        <v>0.2634</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8136</v>
+        <v>-0.161</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1555</v>
+        <v>0.4244</v>
       </c>
       <c r="V2" t="n">
         <v>1.1032</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9487</v>
+        <v>3.7961</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0878</v>
+        <v>0.726</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0365</v>
+        <v>3.0701</v>
       </c>
       <c r="G3" t="n">
         <v>1.6172</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4037</v>
+        <v>1.2511</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6563</v>
+        <v>0.1575</v>
       </c>
       <c r="U3" t="n">
-        <v>1.06</v>
+        <v>1.0936</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6049</v>
+        <v>1.3907</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0725</v>
+        <v>1.8247</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4676</v>
+        <v>-0.434</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0882</v>
@@ -766,13 +766,13 @@
         <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4457</v>
+        <v>1.2316</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0736</v>
+        <v>0.8259</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3721</v>
+        <v>0.4057</v>
       </c>
       <c r="V4" t="n">
         <v>-1.6083</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9789</v>
+        <v>1.1933</v>
       </c>
       <c r="E5" t="n">
-        <v>0.38</v>
+        <v>0.5608</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5989</v>
+        <v>0.6325</v>
       </c>
       <c r="G5" t="n">
         <v>0.7834</v>
@@ -844,13 +844,13 @@
         <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6594</v>
+        <v>0.8738</v>
       </c>
       <c r="T5" t="n">
-        <v>0.13</v>
+        <v>0.3108</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5294</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8278</v>
+        <v>0.575</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6149</v>
+        <v>0.8431</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7872</v>
+        <v>-0.268</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4349</v>
+        <v>-0.5737</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6469</v>
+        <v>-0.9182</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.0818</v>
+        <v>0.3446</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2421</v>
+        <v>0.6383</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4269</v>
+        <v>-0.1814</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1848</v>
+        <v>0.8196</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.677</v>
+        <v>-1.212</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.78</v>
+        <v>-0.7369</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.897</v>
+        <v>-0.4751</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1905</v>
+        <v>0.3833</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4604</v>
+        <v>0.063</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7301</v>
+        <v>0.3203</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>-0.3943</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0644</v>
+        <v>0.453</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2652</v>
+        <v>1.4418</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2008</v>
+        <v>-0.9888</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5737</v>
+        <v>-1.4349</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9182</v>
+        <v>1.6469</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3446</v>
+        <v>-3.0818</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6383</v>
+        <v>1.2421</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1814</v>
+        <v>2.4269</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8196</v>
+        <v>-1.1848</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.212</v>
+        <v>-2.677</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7369</v>
+        <v>-0.78</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4751</v>
+        <v>-1.897</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1274</v>
+        <v>0.8158</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5149</v>
+        <v>0.2873</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3875</v>
+        <v>0.5285</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3943</v>
+        <v>1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3918</v>
+        <v>-0.8904</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-1.5589</v>
       </c>
       <c r="F8" t="n">
-        <v>0.534</v>
+        <v>0.6685</v>
       </c>
       <c r="G8" t="n">
         <v>-1.9127</v>
@@ -1078,13 +1078,13 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2889</v>
+        <v>0.7903</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3566</v>
+        <v>0.7235</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0677</v>
+        <v>0.0668</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4709</v>
+        <v>-3.4246</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4916</v>
+        <v>-0.3109</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.9793</v>
+        <v>-3.1137</v>
       </c>
       <c r="G9" t="n">
         <v>-2.5336</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.08169999999999999</v>
+        <v>-0.0354</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0474</v>
+        <v>0.2282</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1291</v>
+        <v>-0.2636</v>
       </c>
       <c r="V9" t="n">
         <v>0.5361</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3238</v>
+        <v>-4.0058</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7927</v>
+        <v>-1.4075</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5311</v>
+        <v>-2.5983</v>
       </c>
       <c r="G10" t="n">
         <v>-4.279</v>
@@ -1234,13 +1234,13 @@
         <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2768</v>
+        <v>0.0413</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4481</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1713</v>
+        <v>0.1041</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.378</v>
+        <v>-4.0278</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5609</v>
+        <v>-3.9083</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1829</v>
+        <v>-0.1195</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5235</v>
@@ -1312,13 +1312,13 @@
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3053</v>
+        <v>0.6554</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8057</v>
+        <v>-0.1531</v>
       </c>
       <c r="U11" t="n">
-        <v>1.111</v>
+        <v>0.8085</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6213</v>
+        <v>-4.1284</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7579</v>
+        <v>-0.5339</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.8634</v>
+        <v>-3.5946</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7625</v>
@@ -1390,13 +1390,13 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1784</v>
+        <v>0.3145</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1019</v>
+        <v>0.1221</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0764</v>
+        <v>0.1924</v>
       </c>
       <c r="V12" t="n">
         <v>-2.6805</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.883899999999999</v>
+        <v>-4.2702</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4054000000000004</v>
+        <v>3.0191</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.289499999999999</v>
+        <v>-7.2893</v>
       </c>
       <c r="G13" t="n">
         <v>-7.811500000000001</v>
@@ -1468,10 +1468,10 @@
         <v>15.077</v>
       </c>
       <c r="S13" t="n">
-        <v>3.971100000000001</v>
+        <v>6.5851</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2724999999999997</v>
+        <v>2.3414</v>
       </c>
       <c r="U13" t="n">
         <v>4.2437</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4288</v>
+        <v>5.4669</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0785</v>
+        <v>4.4324</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3503</v>
+        <v>1.0345</v>
       </c>
       <c r="G14" t="n">
         <v>4.1255</v>
@@ -1546,13 +1546,13 @@
         <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8411</v>
+        <v>-0.803</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3443</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4968</v>
+        <v>0.1874</v>
       </c>
       <c r="V14" t="n">
         <v>2.1444</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6352</v>
+        <v>3.6644</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8104</v>
+        <v>0.9283</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8248</v>
+        <v>2.7361</v>
       </c>
       <c r="G15" t="n">
         <v>2.6374</v>
@@ -1624,13 +1624,13 @@
         <v>2.5515</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4815</v>
+        <v>-0.4523</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1949</v>
+        <v>-1.0769</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7134</v>
+        <v>0.6247</v>
       </c>
       <c r="V15" t="n">
         <v>-1.0722</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4271</v>
+        <v>2.2419</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7628</v>
+        <v>0.173</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6643</v>
+        <v>2.0689</v>
       </c>
       <c r="G16" t="n">
         <v>2.204</v>
@@ -1702,13 +1702,13 @@
         <v>2.7834</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3286</v>
+        <v>0.1434</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0791</v>
+        <v>-0.5107</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2495</v>
+        <v>0.6541</v>
       </c>
       <c r="V16" t="n">
         <v>1.7501</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8441</v>
+        <v>2.1365</v>
       </c>
       <c r="E17" t="n">
-        <v>1.525</v>
+        <v>1.7609</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3192</v>
+        <v>0.3756</v>
       </c>
       <c r="G17" t="n">
         <v>2.5408</v>
@@ -1780,13 +1780,13 @@
         <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3229</v>
+        <v>-0.0305</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0376</v>
+        <v>-0.8017</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7148</v>
+        <v>0.7712</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1418</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>A. BLAKENEY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0331</v>
+        <v>1.0541</v>
       </c>
       <c r="E18" t="n">
-        <v>4.6073</v>
+        <v>2.7204</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.5742</v>
+        <v>-1.6663</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3874</v>
+        <v>1.515</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1907</v>
+        <v>-1.3625</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.8033</v>
+        <v>2.8774</v>
       </c>
       <c r="J18" t="n">
-        <v>3.0748</v>
+        <v>2.8696</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9276</v>
+        <v>-1.0651</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1472</v>
+        <v>3.9346</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.6874</v>
+        <v>-1.3546</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7369</v>
+        <v>-0.2974</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.9505</v>
+        <v>-1.0572</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8777</v>
+        <v>-0.3165</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6201</v>
+        <v>-0.1491</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-0.1674</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>-1.0722</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BLAKENEY</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3436</v>
+        <v>0.4091</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1307</v>
+        <v>3.3099</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4742</v>
+        <v>-2.9008</v>
       </c>
       <c r="G19" t="n">
-        <v>1.515</v>
+        <v>0.3874</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3625</v>
+        <v>2.1907</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8774</v>
+        <v>-1.8033</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8696</v>
+        <v>3.0748</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0651</v>
+        <v>2.9276</v>
       </c>
       <c r="L19" t="n">
-        <v>3.9346</v>
+        <v>0.1472</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3546</v>
+        <v>-2.6874</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2974</v>
+        <v>-0.7369</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0572</v>
+        <v>-1.9505</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
         <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.7141</v>
+        <v>0.2537</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7389</v>
+        <v>0.3227</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9752</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
         <v>-1.0722</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6661</v>
+        <v>-0.6261</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6821</v>
+        <v>-2.5641</v>
       </c>
       <c r="F20" t="n">
-        <v>2.016</v>
+        <v>1.938</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2505</v>
@@ -2014,13 +2014,13 @@
         <v>2.3195</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2043</v>
+        <v>-0.1643</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9709</v>
+        <v>-0.8529</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.6886</v>
       </c>
       <c r="V20" t="n">
         <v>0.7886</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.74</v>
+        <v>-1.7064</v>
       </c>
       <c r="E21" t="n">
         <v>-0.9026999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8373</v>
+        <v>-0.8037</v>
       </c>
       <c r="G21" t="n">
         <v>-2.1596</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5083</v>
+        <v>-0.4747</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2908</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2175</v>
+        <v>-0.1838</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7346</v>
+        <v>-3.3972</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0403</v>
+        <v>-2.5685</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6943</v>
+        <v>-0.8287</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1885</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1054</v>
+        <v>0.232</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3655</v>
+        <v>0.1063</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2601</v>
+        <v>0.1256</v>
       </c>
       <c r="V22" t="n">
         <v>0.6468</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>6.884</v>
+        <v>9.2432</v>
       </c>
       <c r="E23" t="n">
-        <v>7.2896</v>
+        <v>7.289600000000002</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4054000000000001</v>
+        <v>1.9536</v>
       </c>
       <c r="G23" t="n">
         <v>7.811500000000001</v>
@@ -2248,13 +2248,13 @@
         <v>15.0769</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.9713</v>
+        <v>-1.6122</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.2437</v>
+        <v>-4.2435</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2724999999999997</v>
+        <v>2.6314</v>
       </c>
       <c r="V23" t="n">
         <v>3.0437</v>
